--- a/data/trans_camb/IP11A_R-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/IP11A_R-Estudios-trans_camb.xlsx
@@ -529,14 +529,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,22 +624,22 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>20,03</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>17,51</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>20,03</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -677,7 +677,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 69,91</t>
+          <t>4,97; 52,35</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -692,7 +692,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5,07; 54,07</t>
+          <t>0,0; 66,66</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -707,7 +707,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,79; 42,89</t>
+          <t>4,34; 41,88</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -840,32 +840,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>-4,95</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>-3,07</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>2,25</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>0,0</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>16,67</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>5,35</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-4,95</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-3,07</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,92</t>
+          <t>5,39</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>3,07</t>
+          <t>3,24</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-12,9; -1,32</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4,35; 36,69</t>
+          <t>-10,83; 2,58</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 28,34</t>
+          <t>-6,63; 25,04</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-13,12; -1,3</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-10,38; 2,49</t>
+          <t>4,56; 34,78</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-7,38; 26,07</t>
+          <t>0,0; 28,94</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-9,88; -0,85</t>
+          <t>-8,61; -0,84</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-2,43; 12,05</t>
+          <t>-2,2; 11,91</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-3,46; 17,65</t>
+          <t>-3,3; 17,64</t>
         </is>
       </c>
     </row>
@@ -946,39 +946,39 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>-62,13%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>45,59%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>inf%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>inf%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>-100,0%</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-62,13%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>38,82%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
           <t>121,33%</t>
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>97,4%</t>
+          <t>103,01%</t>
         </is>
       </c>
     </row>
@@ -1034,7 +1034,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-84,31; —</t>
+          <t>-68,96; 1762,11</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1061,27 +1061,27 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
+          <t>10,48</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>7,7</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>0,0</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>14,93</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>0,0</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>10,48</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>8,8</t>
+          <t>13,59</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>11,18</t>
+          <t>10,1</t>
         </is>
       </c>
     </row>
@@ -1114,12 +1114,12 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 42,63</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 69,56</t>
+          <t>0,0; 41,31</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -1129,12 +1129,12 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 41,81</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 42,35</t>
+          <t>0,0; 58,08</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1144,12 +1144,12 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 33,29</t>
+          <t>0,0; 31,16</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 34,47</t>
+          <t>0,0; 33,36</t>
         </is>
       </c>
     </row>
@@ -1167,22 +1167,22 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
+          <t>inf%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>inf%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>—%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1272,32 +1272,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>-0,49</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>-0,73</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>3,07</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>1,37</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>11,77</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>7,83</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>-0,49</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>-0,73</t>
-        </is>
-      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,19</t>
+          <t>7,45</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>5,18</t>
+          <t>4,97</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,19</t>
+          <t>-6,08; 5,61</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>3,27; 26,87</t>
+          <t>-6,41; 6,36</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 25,91</t>
+          <t>-4,26; 21,0</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-6,66; 5,32</t>
+          <t>0,0; 6,85</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-6,85; 6,6</t>
+          <t>3,33; 26,61</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-4,84; 20,77</t>
+          <t>0,0; 23,6</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-3,23; 4,02</t>
+          <t>-3,19; 4,39</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-0,69; 10,27</t>
+          <t>-0,57; 10,45</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-0,19; 15,73</t>
+          <t>-0,78; 14,75</t>
         </is>
       </c>
     </row>
@@ -1378,34 +1378,34 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>-12,46%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>-18,59%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>78,3%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>inf%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>inf%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>inf%</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>-12,46%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>-18,59%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>81,35%</t>
-        </is>
-      </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
           <t>15,74%</t>
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>232,36%</t>
+          <t>222,53%</t>
         </is>
       </c>
     </row>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-45,16; —</t>
+          <t>-51,15; 2258,29</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; —</t>
         </is>
       </c>
     </row>
